--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.01541894061828</v>
+        <v>8.29000557785047</v>
       </c>
       <c r="D2" t="n">
-        <v>36.07553803402584</v>
+        <v>5.862274930529199</v>
       </c>
       <c r="E2" t="n">
-        <v>19.37457575191694</v>
+        <v>3.148368559686503</v>
       </c>
       <c r="F2" t="n">
-        <v>13.16383075375611</v>
+        <v>2.139122497485368</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.89597613746552</v>
+        <v>8.595596122338147</v>
       </c>
       <c r="D3" t="n">
-        <v>36.8226790032783</v>
+        <v>5.983685338032723</v>
       </c>
       <c r="E3" t="n">
-        <v>19.37457575191694</v>
+        <v>3.148368559686503</v>
       </c>
       <c r="F3" t="n">
-        <v>13.16383075375611</v>
+        <v>2.139122497485368</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.56511817033836</v>
+        <v>8.054331702679983</v>
       </c>
       <c r="D4" t="n">
-        <v>31.69933508255057</v>
+        <v>5.151141950914467</v>
       </c>
       <c r="E4" t="n">
-        <v>19.37457575191694</v>
+        <v>3.148368559686503</v>
       </c>
       <c r="F4" t="n">
-        <v>13.16383075375611</v>
+        <v>2.139122497485368</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.57660191919474</v>
+        <v>1.881197811869145</v>
       </c>
       <c r="D5" t="n">
-        <v>11.37522726001652</v>
+        <v>1.848474429752685</v>
       </c>
       <c r="E5" t="n">
-        <v>19.37457575191694</v>
+        <v>3.148368559686503</v>
       </c>
       <c r="F5" t="n">
-        <v>13.16383075375611</v>
+        <v>2.139122497485368</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>74.48731862062429</v>
+        <v>12.10418927585145</v>
       </c>
       <c r="D6" t="n">
-        <v>56.17558277215002</v>
+        <v>9.128532200474378</v>
       </c>
       <c r="E6" t="n">
-        <v>19.37457575191694</v>
+        <v>3.148368559686503</v>
       </c>
       <c r="F6" t="n">
-        <v>13.16383075375611</v>
+        <v>2.139122497485368</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>62.9493280446457</v>
+        <v>10.22926580725493</v>
       </c>
       <c r="D7" t="n">
-        <v>39.25914269942515</v>
+        <v>6.379610688656588</v>
       </c>
       <c r="E7" t="n">
-        <v>19.37457575191694</v>
+        <v>3.148368559686503</v>
       </c>
       <c r="F7" t="n">
-        <v>13.16383075375611</v>
+        <v>2.139122497485368</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
